--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0037.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0037.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Mistcloak Strike</t>
+          <t>Đòn Đánh Áo Sương</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Windborne Rider</t>
+          <t>Kỵ Sĩ Gió Bay</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Jianxin's Nickname</t>
+          <t>Biệt danh của Jianxin</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Vessel of Sounds</t>
+          <t>Vỏ Âm Thanh</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Vessel of Sounds</t>
+          <t>Vỏ Âm Thanh</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Nature Calling</t>
+          <t>Tiếng Gọi Của Tự Nhiên</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Power of Xuanwu</t>
+          <t>Sức Mạnh Huyền Vũ</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Scarlet Shade</t>
+          <t>Bóng Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Vessel of Sounds</t>
+          <t>Vỏ Âm Thanh</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Vessel of Sounds</t>
+          <t>Vỏ Âm Thanh</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Echo Character-Cruisewing</t>
+          <t>Tiếng Vọng Nhân Vật: Cánh Tuần Dực</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Zapstring</t>
+          <t>Dây Sét</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Echo Character-Zapstring</t>
+          <t>Tiếng Vọng Nhân Vật: Dây Tia Chớp</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Echo Character-Excarat</t>
+          <t>Tiếng Vọng Nhân Vật: Excarat</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Echo Character-Stonewall bracer</t>
+          <t>Tiếng Vọng Nhân Vật: Băng Tay Đá Tảng</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Echo Character-Gulpuff</t>
+          <t>Tiếng Vọng Nhân Vật: Gulpuff</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Echo Character-Gulpuff</t>
+          <t>Tiếng Vọng Nhân Vật: Gulpuff</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Echo Character-Crownless</t>
+          <t>Tiếng Vọng Nhân Vật: Vô Đỉnh</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Snow Waltz</t>
+          <t>Điệu Valse Tuyết</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Snow Waltz</t>
+          <t>Điệu Valse Tuyết</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Snow Waltz</t>
+          <t>Điệu Valse Tuyết</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Execution fRover</t>
+          <t>Lỗi Thi Hành fRover</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Female Rover cho Finishing Attack</t>
+          <t>Vận Mệnh Giả - Hoàn Thành Đòn Tấn Công</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Female Rover cho Finishing Attack</t>
+          <t>Vận Mệnh Giả - Hoàn Thành Đòn Tấn Công</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Execution mRover</t>
+          <t>Lỗi Thi Hành mRover</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Male Rover cho Finishing Attack</t>
+          <t>Vận Mệnh Giả thực hiện Đòn Kết Thúc</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Male Rover cho Finishing Attack</t>
+          <t>Vận Mệnh Giả thực hiện Đòn Kết Thúc</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>EncoreCharacter task</t>
+          <t>Nhiệm vụ nhân vật Encore</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>JiyanCharacter mission</t>
+          <t>Nhiệm vụ nhân vật Jiyan</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>YinlinCharacter mission</t>
+          <t>Nhiệm vụ nhân vật Yinlin</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>LingyangCharacter mission</t>
+          <t>Nhiệm vụ nhân vật Lingyang</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Silent Icefield</t>
+          <t>Băng Nguyên Vô Thanh</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>YangyangCharacter mission</t>
+          <t>Nhiệm vụ nhân vật Yangyang</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>ChixiaCharacter mission</t>
+          <t>Nhiệm vụ nhân vật Chixia</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi hoàn thành độ khó trước đó</t>
+          <t>Mở khóa sau khi hoàn thành Độ Khó trước đó</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Giảm giá</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>well worthwhile</t>
+          <t>thật xứng đáng</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Được đề xuất</t>
+          <t>Đề xuất</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Tự do</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Đặc Biệt</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>New Voyage</t>
+          <t>Hành trình mới</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Weapon Shop</t>
+          <t>Cửa Hàng Vũ Khí</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Shifang Pharmacy</t>
+          <t>Dược Phẩm Shifang</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Souvenir Cửa hàng</t>
+          <t>Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Waveplates Exchange</t>
+          <t>Đổi Bảng Tần Số</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Mahe's Grocery</t>
+          <t>Cửa Hàng Tạp Hóa Mahe</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Panhua's Restaurant</t>
+          <t>Nhà Hàng Panhua</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Tiger's Maw Ore</t>
+          <t>Quặng Hàm Hổ</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tiger's Maw Eatery</t>
+          <t>Quán Ăn Hàm Hổ</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Yibai Clinic</t>
+          <t>Phòng Khám Yibai</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Yumyum Haven</t>
+          <t>Thiên Đường Ẩm Thực</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Fireworks Cửa hàng</t>
+          <t>Cửa tiệm pháo hoa</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Wishing Stall</t>
+          <t>Gian Hàng Ước Nguyện</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>KU-Money Exchange</t>
+          <t>Sàn Giao Dịch KU-Money</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Rosemary's Apothecary</t>
+          <t>Hiệu Thuốc Của Rosemary</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Rosemary's Apothecary</t>
+          <t>Hiệu Thuốc Của Rosemary</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Trattoria Margherita</t>
+          <t>Quán Trattoria Margherita</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Trattoria Margherita</t>
+          <t>Quán Trattoria Margherita</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Averardo Bank Counter</t>
+          <t>Quầy Giao Dịch Ngân Hàng Averardo</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Averardo Bank Counter</t>
+          <t>Quầy Giao Dịch Ngân Hàng Averardo</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Masks &amp; Garments [Masked Reverie]</t>
+          <t>Mặt Nạ &amp; Trang Phục [Mộng Ảo Đeo Mặt Nạ]</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Stillwind Sundries</t>
+          <t>Cửa Hàng Stillwind</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Stillwind Sundries</t>
+          <t>Cửa Hàng Stillwind</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Burrata Bakery</t>
+          <t>Tiệm Bánh Burrata</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Burrata Bakery</t>
+          <t>Tiệm Bánh Burrata</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Cruise Share</t>
+          <t>Chia sẻ Cruise</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Rinascita Sonance Casket Collector</t>
+          <t>Nhà Sưu Tầm Hòm Sonance Rinascita</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>7号无音区</t>
+          <t>Tổ Tacet Số 7</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>8号无音区</t>
+          <t>Khu Vô Âm Số 8</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Combusting Variation</t>
+          <t>Biến Thể Đốt Cháy</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Stagnant Dimension</t>
+          <t>Không Gian Trì Trệ</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Stygian Thunder</t>
+          <t>Sấm Sét Stygian</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Fountain of Concerto</t>
+          <t>Suối Giao Hưởng</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Fountain of Zephyr</t>
+          <t>Suối Gió Nhẹ</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Incessant Zephyr</t>
+          <t>Cơn Gió Vô Tận</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Fountain of Explosion</t>
+          <t>Suối Bùng Nổ</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Secondary Deflagration</t>
+          <t>Đợt Nổ Phụ</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Resonance Abound</t>
+          <t>Cộng Hưởng Dâng Trào</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Ebbing Tides</t>
+          <t>Triều Xuống</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Zephyr Protection</t>
+          <t>Hộ Mệnh Zephyr</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Raging Zephyr</t>
+          <t>Gió Cuồng Nộ</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Fountain of Frost</t>
+          <t>Suối Băng Giá</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>absolute zero</t>
+          <t>số không tuyệt đối</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>SOLD OUT</t>
+          <t>HẾT HÀNG</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Sort theo Mức Đe Dọa</t>
+          <t>Sắp xếp theo Mức Đe Dọa</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Main: Healing Bonus</t>
+          <t>Chủ: Hiệu Quả Hồi Phục+</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Sort theo ID Item</t>
+          <t>Sắp xếp theo ID Vật Phẩm</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Sort theo Cấp độ</t>
+          <t>Sắp xếp theo Cấp Độ</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Sort theo Cấp độ</t>
+          <t>Sắp xếp theo Cấp Độ</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Main: Energy Regen</t>
+          <t>Chính: Hồi Phục Năng Lượng</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Sort theo Cấp độ</t>
+          <t>Sắp xếp theo Cấp Độ</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Sort theo Status Điều chỉnh</t>
+          <t>Sắp xếp theo Trạng Thái Điều Chỉnh</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Sort theo Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Show Available Item First</t>
+          <t>Hiển Thị Vật Phẩm Có Sẵn Trước</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Sort theo Loại</t>
+          <t>Sắp xếp theo Loại</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Sub: Healing Bonus</t>
+          <t>Phụ: Hiệu Quả Hồi Phục+</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Sort theo Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Sort theo Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Sort theo Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sort theo Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sort theo Rarity</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Sort theo ID Item</t>
+          <t>Sắp xếp theo ID Vật Phẩm</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Sort theo EXP Cơ bản</t>
+          <t>Sắp xếp theo Kinh Nghiệm Cơ Bản</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Sort theo EXP Cơ bản</t>
+          <t>Sắp xếp theo Kinh Nghiệm Cơ Bản</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Show EXP Material First</t>
+          <t>Ưu tiên Hiển thị Nguyên liệu Kinh nghiệm</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Show Unequipped First</t>
+          <t>Ưu tiên hiển thị Tiếng Vọng chưa trang bị</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Show Equipped First</t>
+          <t>Ưu tiên Hiển thị Trang bị Đã mặc</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Show Owned First</t>
+          <t>Ưu tiên hiển thị vật phẩm đã sở hữu</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Sub: Energy Regen</t>
+          <t>Hồi Phục Năng Lượng</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Sort theo số lượng</t>
+          <t>Sắp xếp theo Số Lượng</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Monster Sorting ID</t>
+          <t>ID sắp xếp quái vật</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Sort theo ID vật phẩm</t>
+          <t>Sắp xếp theo ID Vật Phẩm</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Sort theo thời gian thêm</t>
+          <t>Sắp xếp theo Thời Gian Thêm</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sort theo độ hiếm</t>
+          <t>Sắp xếp theo Độ Hiếm</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Sort theo thứ tự nhận được</t>
+          <t>Sắp xếp theo Thứ Tự Nhận</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Sort theo độ thân mật</t>
+          <t>Sắp xếp theo Mức Thân Tình</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Sort theo tiến độ EXP</t>
+          <t>Sắp xếp theo Tiến Độ Kinh Nghiệm</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Sort theo ID vật phẩm</t>
+          <t>Sắp xếp theo ID Vật Phẩm</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Sort theo mức độ đe dọa</t>
+          <t>Sắp xếp theo Mức Đe Dọa</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sort theo cấp độ Hợp Tấu</t>
+          <t>Sắp xếp theo Cấp Đồng Điệu</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Sort theo Vigor</t>
+          <t>Sắp xếp theo Sinh Lực</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Sort theo ID vật phẩm</t>
+          <t>Sắp xếp theo ID Vật Phẩm</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Sort theo vị trí</t>
+          <t>Sắp xếp theo Vị Trí</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Show Phantom Echoes First</t>
+          <t>Ưu tiên hiển thị Tiếng Vọng Ảo</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Show Discarded First</t>
+          <t>Ưu tiên Hiển thị Vật phẩm Bị loại bỏ</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>5-Star First</t>
+          <t>Cộng Hưởng Giả 5 Sao Đầu Tiên</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Unleveled First</t>
+          <t>Thứ Hạng Chưa Nâng Cấp Đầu Tiên</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Cơ chế Đặc biệt</t>
+          <t>Cơ Chế Đặc Biệt</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Novice Pharmacist</t>
+          <t>Dược Sĩ Tân Thủ</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Assistant Pharmacist</t>
+          <t>Phụ tá Dược sĩ</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Resonance Waltz</t>
+          <t>Điệu Waltz Cộng Hưởng</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Song of Feathers</t>
+          <t>Khúc Ca Lông Vũ</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Tầng này không có hiệu ứng khu vực</t>
+          <t>Tầng này không có Hiệu Ứng Khu Vực</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Physical Training I</t>
+          <t>Huấn luyện Vật lý I</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Physical Training I</t>
+          <t>Huấn luyện Vật lý I</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Physical Training II</t>
+          <t>Huấn luyện Vật lý II</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Physical Training II</t>
+          <t>Huấn luyện Vật lý II</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Physical Training III</t>
+          <t>Huấn luyện Vật lý III</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Physical Training III</t>
+          <t>Huấn luyện Vật lý III</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Physical Training IV</t>
+          <t>Huấn luyện Vật lý IV</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Physical Training IV</t>
+          <t>Huấn luyện Vật lý IV</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Combat Training I</t>
+          <t>Huấn Luyện Chiến Đấu I</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Combat Training I</t>
+          <t>Huấn Luyện Chiến Đấu I</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Combat Training II</t>
+          <t>Huấn Luyện Chiến Đấu II</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Combat Training II</t>
+          <t>Huấn Luyện Chiến Đấu II</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Combat Training III</t>
+          <t>Huấn Luyện Chiến Đấu III</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Combat Training III</t>
+          <t>Huấn Luyện Chiến Đấu III</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Combat Training IV</t>
+          <t>Huấn Luyện Chiến Đấu IV</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Combat Training IV</t>
+          <t>Huấn Luyện Chiến Đấu IV</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation I</t>
+          <t>Mô Phỏng Chiến Đấu Cấp I</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation I</t>
+          <t>Mô Phỏng Chiến Đấu Cấp I</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation II</t>
+          <t>Mô Phỏng Chiến Đấu Cấp II</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation II</t>
+          <t>Mô Phỏng Chiến Đấu Cấp II</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation III</t>
+          <t>Mô Phỏng Chiến Đấu Cấp III</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation III</t>
+          <t>Mô Phỏng Chiến Đấu Cấp III</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation IV</t>
+          <t>Mô Phỏng Chiến Đấu Cấp IV</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Mock Battle Simulation IV</t>
+          <t>Mô Phỏng Chiến Đấu Cấp IV</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Integrated Training I</t>
+          <t>Huấn luyện Tích hợp I</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Integrated Training I</t>
+          <t>Huấn luyện Tích hợp I</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>basic single team challenge</t>
+          <t>thử thách đội đơn cơ bản</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>final single team challenge</t>
+          <t>thử thách đơn đội cuối cùng</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>basic dual team challenge</t>
+          <t>thử thách đội kép cơ bản</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>final double team challenge</t>
+          <t>thử thách song đấu cuối cùng</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>shallow description text</t>
+          <t>mô tả sơ lược</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>shallow title description</t>
+          <t>mô tả tiêu đề tóm tắt</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất</t>
+          <t>Huấn luyện Vật lý</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất</t>
+          <t>Huấn luyện Vật lý</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18776,7 +18776,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Middle level description text</t>
+          <t>Mô tả cấp trung</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>middle level title description</t>
+          <t>mô tả tiêu đề cấp trung</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Combat Tests</t>
+          <t>Thử Nghiệm Chiến Đấu</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Combat Tests</t>
+          <t>Thử Nghiệm Chiến Đấu</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>deep description text</t>
+          <t>mô tả chi tiết chuyên sâu</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>deep title description</t>
+          <t>mô tả tiêu đề chuyên sâu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Simulated Battle</t>
+          <t>Trận Chiến Mô Phỏng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Simulated Battle</t>
+          <t>Trận Chiến Mô Phỏng</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>deep description text</t>
+          <t>mô tả chi tiết chuyên sâu</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>deep title description</t>
+          <t>mô tả tiêu đề chuyên sâu</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Comprehensive Mock Battle</t>
+          <t>Trận Giả Chiến Toàn Diện</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Comprehensive Mock Battle</t>
+          <t>Trận Giả Chiến Toàn Diện</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Điểm Số</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Fusion Boost</t>
+          <t>Tăng Cường Hợp Nhất</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Fusion Boost</t>
+          <t>Tăng Cường Hợp Nhất</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19896,7 +19896,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Electro Boost</t>
+          <t>Tăng Cường Electro</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19966,7 +19966,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Electro Boost</t>
+          <t>Tăng Cường Electro</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Aero Boost</t>
+          <t>Tăng cường Aero</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Aero Boost</t>
+          <t>Tăng cường Aero</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Glacio Boost</t>
+          <t>Tăng Cường Glacio</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Glacio Boost</t>
+          <t>Tăng Cường Glacio</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Enhanced Burn</t>
+          <t>Thiêu Đốt Cường Hóa</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Enhanced Burn</t>
+          <t>Thiêu Đốt Cường Hóa</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Enhanced Frozen</t>
+          <t>Đóng Băng Cường Hóa</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Enhanced Frozen</t>
+          <t>Đóng Băng Cường Hóa</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Enhanced Paralysis</t>
+          <t>Tê Liệt Nâng Cao</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Enhanced Paralysis</t>
+          <t>Tê Liệt Nâng Cao</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Bổ Sung Túi đồ</t>
+          <t>Ba Lô Phụ</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Bounty Hunter</t>
+          <t>Thợ Săn Tiền Thưởng</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Fixed Yield</t>
+          <t>Năng suất cố định</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Streamlined Logistics</t>
+          <t>Hậu cần Tối ưu</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Bonus Service</t>
+          <t>Dịch Vụ Phần Thưởng</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21086,7 +21086,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Machine Optimization</t>
+          <t>Tối ưu hóa thiết bị</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Fortune Fairy</t>
+          <t>Tiên May Mắn</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Power Overload</t>
+          <t>Quá Tải Năng Lượng</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Tất cả or Nothing</t>
+          <t>Tất Cả Hoặc Không Gì Cả</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21366,7 +21366,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Không Retreat</t>
+          <t>Không Rút Lui</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Storage Expansion</t>
+          <t>Mở Rộng Kho Lưu Trữ</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Logistics Optimization</t>
+          <t>Tối Ưu Hóa Hậu Cần</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Supply Replenishment</t>
+          <t>Bổ Sung Vật Tư</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Wall Boost</t>
+          <t>Tăng Tốc Tường</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Wall Boost</t>
+          <t>Tăng Tốc Tường</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Ceiling Boost</t>
+          <t>Tăng Tốc Trần Nhà</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Ceiling Boost</t>
+          <t>Tăng Tốc Trần Nhà</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Ground Boost</t>
+          <t>Tăng tốc Mặt đất</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Ground Boost</t>
+          <t>Tăng tốc Mặt đất</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Snail Tactics</t>
+          <t>Chiến thuật Ốc Sên</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Snail Tactics</t>
+          <t>Chiến thuật Ốc Sên</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Suppression Tactics</t>
+          <t>Chiến Thuật Áp Chế</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Suppression Tactics</t>
+          <t>Chiến Thuật Áp Chế</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Electro Synergy</t>
+          <t>Đồng Bộ Điện</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Electro Synergy</t>
+          <t>Đồng Bộ Điện</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Glacio Synergy</t>
+          <t>Hiệu Ứng Glacio</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Glacio Synergy</t>
+          <t>Hiệu Ứng Glacio</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Energy Divergence</t>
+          <t>Sự Phân Kỳ Năng Lượng</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Energy Divergence</t>
+          <t>Sự Phân Kỳ Năng Lượng</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Exposed Weakness</t>
+          <t>Điểm Yếu Bị Phơi Bày</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Exposed Weakness</t>
+          <t>Điểm Yếu Bị Phơi Bày</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Final Burst</t>
+          <t>Đòn Tấn Công Cuối</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Final Burst</t>
+          <t>Đòn Tấn Công Cuối</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Out of Moves</t>
+          <t>Hết nước đi</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23116,7 +23116,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Out of Moves</t>
+          <t>Hết nước đi</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Efficient Execution</t>
+          <t>Thi Hành Hiệu Quả</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23256,7 +23256,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Efficient Execution</t>
+          <t>Thi Hành Hiệu Quả</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Chill Conduction</t>
+          <t>Dẫn truyền lạnh</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Chill Conduction</t>
+          <t>Dẫn truyền lạnh</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Lean Mode</t>
+          <t>Chế Độ Tựa</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Lean Mode</t>
+          <t>Chế Độ Tựa</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Every Bit Counts</t>
+          <t>Từng Chi Tiết Đều Quan Trọng</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Every Bit Counts</t>
+          <t>Từng Chi Tiết Đều Quan Trọng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Negotiation Strategy</t>
+          <t>Chiến thuật Đàm phán</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Negotiation Strategy</t>
+          <t>Chiến thuật Đàm phán</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23886,7 +23886,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Under the Table</t>
+          <t>Dưới gầm bàn</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Under the Table</t>
+          <t>Dưới gầm bàn</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Budget Optimization</t>
+          <t>Tối Ưu Ngân Sách</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Budget Optimization</t>
+          <t>Tối Ưu Ngân Sách</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Midas Touch</t>
+          <t>Bàn Tay Midas</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Midas Touch</t>
+          <t>Bàn Tay Midas</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Money Talks</t>
+          <t>Tiền bạc lên tiếng</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Money Talks</t>
+          <t>Tiền bạc lên tiếng</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Overflowing Fortune</t>
+          <t>May Mắn Tràn Đầy</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Overflowing Fortune</t>
+          <t>May Mắn Tràn Đầy</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Overhead Strike</t>
+          <t>Đòn Đánh Từ Trên Cao</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Overhead Strike</t>
+          <t>Đòn Đánh Từ Trên Cao</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Echo Boost (Fusion)</t>
+          <t>Tăng Cường Echo (Fusion)</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Echo Boost (Fusion)</t>
+          <t>Tăng Cường Echo (Fusion)</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Echo Boost (Electro)</t>
+          <t>Tăng Cường Echo (Electro)</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25076,7 +25076,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Echo Boost (Electro)</t>
+          <t>Tăng Cường Echo (Electro)</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Echo Boost (Glacio)</t>
+          <t>Tăng Cường Echo (Glacio)</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25216,7 +25216,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Echo Boost (Glacio)</t>
+          <t>Tăng Cường Echo (Glacio)</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Echo Boost (Aero)</t>
+          <t>Tăng Cường Echo (Aero)</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Echo Boost (Aero)</t>
+          <t>Tăng Cường Echo (Aero)</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Mimic in the Chest</t>
+          <t>Quái Giả Hình Trong Rương</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Mimic in the Chest</t>
+          <t>Quái Giả Hình Trong Rương</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Explosive Junrock</t>
+          <t>Đá Jun Nổ</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Explosive Junrock</t>
+          <t>Đá Jun Nổ</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Superpuff</t>
+          <t>Siêu Bông Xốp</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Superpuff</t>
+          <t>Siêu Bông Xốp</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dancing Hoartoise</t>
+          <t>Hoartoise nhảy múa</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Dancing Hoartoise</t>
+          <t>Hoartoise nhảy múa</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Unknown Location</t>
+          <t>Nơi không tên</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26056,7 +26056,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Sonata Effect</t>
+          <t>Hiệu Ứng Sonata</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26196,7 +26196,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>High Rarity</t>
+          <t>Hiếm Có</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26266,7 +26266,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Higher Rarity</t>
+          <t>Độ hiếm cao hơn</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Nâng cấp lên +5 để mở khóa Echo Tuning</t>
+          <t>Nâng cấp lên +5 để mở khóa Điều Chỉnh Echo</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Nâng cấp lên +10 để mở khóa Tuning</t>
+          <t>Nâng cấp lên +10 để mở khóa Điều Chỉnh</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26476,7 +26476,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Not equipped to Main Slot</t>
+          <t>Chưa trang bị vào Khe Chính</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Chọn vật liệu</t>
+          <t>Chọn nguyên liệu</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>New Tuning Slot</t>
+          <t>Khe Điều Chỉnh mới</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>EXP needed for Tuning</t>
+          <t>EXP cần thiết cho Điều Chỉnh</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Sẽ được Tuning</t>
+          <t>Để được Điều Chỉnh</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>SOL3 Thăng Tiến Pha available</t>
+          <t>Thăng Hoa Giai Đoạn SOL3 đã mở khóa</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Mở Khóa Echo Mới</t>
+          <t>Echo Mới Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Health is full</t>
+          <t>HP đã đầy</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27036,7 +27036,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Practitioner Doctor</t>
+          <t>Bác sĩ Thực Nghiệm</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27106,7 +27106,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Expert Pharmacist</t>
+          <t>Dược Sư Lão Luyện</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27176,7 +27176,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Danh hiệu này được trao cho những người đã tinh thông nhiều nguyên lý bào chế dược phẩm</t>
+          <t>Danh hiệu này được trao cho những người đã tinh thông các nguyên lý bào chế dược phẩm.</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27246,7 +27246,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Master Pharmacist</t>
+          <t>Dược Sư trưởng</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Rarity</t>
+          <t>Độ Hiếm</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>1-Star</t>
+          <t>1 Sao</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>2-Stars</t>
+          <t>2 Sao</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27526,7 +27526,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>3-Stars</t>
+          <t>3 Sao</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>4-Stars</t>
+          <t>4 Sao</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>5-Stars</t>
+          <t>5 Sao</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27736,7 +27736,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Phần Thưởng Nhiệm Vụ</t>
+          <t>Phần thưởng nhiệm vụ</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Basic Training</t>
+          <t>Huấn Luyện Cơ Bản</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Resonator Combat Training</t>
+          <t>Huấn Luyện Chiến Đấu Resonator</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28016,7 +28016,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28156,7 +28156,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Basic Lineup Combat</t>
+          <t>Chiến Đấu Đội Hình Cơ Bản</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Các Echoes giống nhau sẽ không được tính vào hiệu ứng Sonata</t>
+          <t>Hồi Âm giống nhau sẽ không được tính vào hiệu ứng Sonata</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Echo Skills: Countermeasures</t>
+          <t>Kỹ Năng Hồi Âm: Phản Công Chiến Lược</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28436,7 +28436,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Rewards được xác định theo cấp Data Bank và Giai đoạn SOL3</t>
+          <t>Phần thưởng được quyết định bởi cấp độ Kho Dữ Liệu và Giai Đoạn SOL3 của bạn</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28576,7 +28576,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Difficult</t>
+          <t>Khó nhằn thật</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 5.000 điểm</t>
+          <t>Thu thập tổng cộng 5.000 điểm</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28786,7 +28786,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 10.000 điểm</t>
+          <t>Đạt tổng cộng 10.000 điểm</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28856,7 +28856,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 15.000 điểm</t>
+          <t>Tổng cộng đạt 15.000 điểm.</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 20.000 điểm</t>
+          <t>Thu thập tổng cộng 20.000 điểm</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 30.000 điểm</t>
+          <t>Tổng cộng đạt 30.000 điểm.</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 50.000 điểm</t>
+          <t>Đạt tổng cộng 50.000 điểm</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29136,7 +29136,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 70.000 điểm</t>
+          <t>Đạt tổng cộng 70.000 điểm</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 90.000 điểm</t>
+          <t>Thu thập tổng cộng 90.000 điểm.</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 10.000 điểm</t>
+          <t>Đạt tổng cộng 10.000 điểm</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29346,7 +29346,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 20.000 điểm</t>
+          <t>Thu thập tổng cộng 20.000 điểm</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29416,7 +29416,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 40.000 điểm</t>
+          <t>Đạt tổng cộng 40.000 điểm.</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 60.000 điểm</t>
+          <t>Đạt tổng cộng 60.000 điểm</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29556,7 +29556,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 70.000 điểm</t>
+          <t>Đạt tổng cộng 70.000 điểm</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 80.000 điểm</t>
+          <t>Đạt tổng cộng 80.000 điểm</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Tổng cộng đạt 90.000 điểm</t>
+          <t>Thu thập tổng cộng 90.000 điểm.</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29766,7 +29766,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Breath Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Hơi Thở</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29836,7 +29836,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Freezing Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Băng Giá</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Scorching Rift</t>
+          <t>Đạt 2.000 điểm trong Scorching Rift</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Rapido Rift</t>
+          <t>Đạt 2.000 điểm trong Rapido Rift</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30046,7 +30046,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Striking Rift</t>
+          <t>Đạt 2.000 điểm trong Striking Rift</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Intimidating Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Uy Hiếp</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30186,7 +30186,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Deafening Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Chấn Động</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Furious Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Cuồng Nộ</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Ethereal Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Hư Ảo</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Everlasting Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Rupture Rift</t>
+          <t>Đạt 2.000 điểm trong Rupture Rift</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30536,7 +30536,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Empyrean Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Thiên Giới</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Aftersound Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Dư Âm</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Fervor Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Nóng Bỏng</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Crescent Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Lưỡi Liềm</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Stagnation Rift</t>
+          <t>Đạt 2.000 điểm trong Stagnation Rift</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm tại Devouring Rift</t>
+          <t>Đạt 2.000 điểm trong Tổ Tacet Nuốt Chửng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hiện không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Đạt Cấp Data Bank 10</t>
+          <t>Đạt Cấp Ngân Hàng Dữ Liệu 10.</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Complete "Silver-haired Echo Trainer"</t>
+          <t>Hoàn thành "Huấn Luyện Viên Tóc Bạc Vang Vọng"</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Xem Data Bank của bạn</t>
+          <t>Xem Kho Dữ Liệu Của Bạn</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Di chuyển về trước</t>
+          <t>Tiến lên.</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Move backward</t>
+          <t>Lùi lại đi.</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Move left</t>
+          <t>Rẽ trái.</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Walk/Run (Toggle)</t>
+          <t>Đi/Chạy (Bật/Tắt)</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Lock mục tiêu</t>
+          <t>Khóa mục tiêu</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Disable Mục tiêu Lock (Giữ)</t>
+          <t>Vô Hiệu Hóa Khóa Mục Tiêu (Giữ)</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Dash/Dodge</t>
+          <t>Lao/Né tránh</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Dash/Dodge</t>
+          <t>Lao/Né tránh</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Sử dụng Công cụ</t>
+          <t>Sử dụng Tiện Ích</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Công cụ Wheel</t>
+          <t>Bánh xe tiện ích</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32356,7 +32356,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Chuyển sang Chế độ Nhắm</t>
+          <t>Chuyển sang Chế Độ Nhắm</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Drop xuống khi leo</t>
+          <t>Thả Xuống Khi Leo</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Pick Up/Interact</t>
+          <t>Nhặt Lên/Tương Tác</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32636,7 +32636,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 1</t>
+          <t>Đổi sang Thành viên 1</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32706,7 +32706,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 2</t>
+          <t>Đổi sang Thành viên 2</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 3</t>
+          <t>Đổi sang Thành viên 3</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 4</t>
+          <t>Chuyển sang Thành viên Đội 4</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32916,7 +32916,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Theo dõi Nhiệm vụ</t>
+          <t>Nhiệm vụ bản nhạc</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32986,7 +32986,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Quit Thử thách</t>
+          <t>Thoát Thử Thách</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33196,7 +33196,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Quick Access Wheel</t>
+          <t>Bánh xe truy cập nhanh</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Chỉnh sửa</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Công cụ Wheel</t>
+          <t>Bánh xe tiện ích</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Move left or right</t>
+          <t>Di chuyển sang trái hoặc phải</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Move forward or backward</t>
+          <t>Tiến lên hoặc lùi lại.</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Move left or right</t>
+          <t>Di chuyển sang trái hoặc phải</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33826,7 +33826,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Lock mục tiêu</t>
+          <t>Khóa mục tiêu</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Lock mục tiêu</t>
+          <t>Khóa mục tiêu</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33966,7 +33966,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Disable Mục tiêu Lock (Giữ)</t>
+          <t>Vô Hiệu Hóa Khóa Mục Tiêu (Giữ)</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Disable Mục tiêu Lock (Giữ)</t>
+          <t>Vô Hiệu Hóa Khóa Mục Tiêu (Giữ)</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Đặt lại Camera</t>
+          <t>Đặt lại góc quay</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đặt lại Camera</t>
+          <t>Đặt lại góc quay</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Dash/Dodge</t>
+          <t>Lao/Né tránh</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dash/Dodge</t>
+          <t>Lao/Né tránh</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34666,7 +34666,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Sử dụng Công cụ</t>
+          <t>Sử dụng Tiện Ích</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Sử dụng Công cụ</t>
+          <t>Sử dụng Tiện Ích</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Chuyển sang Chế độ Nhắm</t>
+          <t>Chuyển sang Chế Độ Nhắm</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Chuyển sang Chế độ Nhắm</t>
+          <t>Chuyển sang Chế Độ Nhắm</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35086,7 +35086,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Attack when Aiming</t>
+          <t>Tấn Công khi Ngắm bắn</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35156,7 +35156,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Attack when Aiming</t>
+          <t>Tấn Công khi Ngắm bắn</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Drop Down when Climbing</t>
+          <t>Thả Xuống Khi Leo</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Drop Down when Climbing</t>
+          <t>Thả Xuống Khi Leo</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Pick Up/Interact</t>
+          <t>Nhặt Lên/Tương Tác</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
